--- a/apps/homework-wordcloud/sample_input/19990102.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990102.xlsx
@@ -1708,12 +1708,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>411194059</t>
+          <t>990094059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>411194059@gms.ndhu.edu.tw</t>
+          <t>990094059@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>411185750</t>
+          <t>990085750</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>411185750@gms.ndhu.edu.tw</t>
+          <t>990085750@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>411123578</t>
+          <t>990023578</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>411123578@gms.ndhu.edu.tw</t>
+          <t>990023578@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>411137045</t>
+          <t>990037045</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>411137045@gms.ndhu.edu.tw</t>
+          <t>990037045@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>411123457</t>
+          <t>990023457</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>411123457@gms.ndhu.edu.tw</t>
+          <t>990023457@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>411153669</t>
+          <t>990053669</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>411153669@gms.ndhu.edu.tw</t>
+          <t>990053669@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>411112230</t>
+          <t>990012230</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>411112230@gms.ndhu.edu.tw</t>
+          <t>990012230@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>411162982</t>
+          <t>990062982</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>411162982@gms.ndhu.edu.tw</t>
+          <t>990062982@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>411148558</t>
+          <t>990048558</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>411148558@gms.ndhu.edu.tw</t>
+          <t>990048558@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>411127143</t>
+          <t>990027143</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>411127143@gms.ndhu.edu.tw</t>
+          <t>990027143@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>411183314</t>
+          <t>990083314</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>411183314@gms.ndhu.edu.tw</t>
+          <t>990083314@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>411168730</t>
+          <t>990068730</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>411168730@gms.ndhu.edu.tw</t>
+          <t>990068730@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>411130882</t>
+          <t>990030882</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>411130882@gms.ndhu.edu.tw</t>
+          <t>990030882@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>411115245</t>
+          <t>990015245</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>411115245@gms.ndhu.edu.tw</t>
+          <t>990015245@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>411118170</t>
+          <t>990018170</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>411118170@gms.ndhu.edu.tw</t>
+          <t>990018170@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>411124949</t>
+          <t>990024949</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>411124949@gms.ndhu.edu.tw</t>
+          <t>990024949@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>411130142</t>
+          <t>990030142</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>411130142@gms.ndhu.edu.tw</t>
+          <t>990030142@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>411135584</t>
+          <t>990035584</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>411135584@gms.ndhu.edu.tw</t>
+          <t>990035584@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>411142934</t>
+          <t>990042934</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>411142934@gms.ndhu.edu.tw</t>
+          <t>990042934@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>411195101</t>
+          <t>990095101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>411195101@gms.ndhu.edu.tw</t>
+          <t>990095101@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>411111664</t>
+          <t>990011664</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>411111664@gms.ndhu.edu.tw</t>
+          <t>990011664@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>411146562</t>
+          <t>990046562</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>411146562@gms.ndhu.edu.tw</t>
+          <t>990046562@gms.ndhu.edu.tw</t>
         </is>
       </c>
       <c r="E23" t="n">

--- a/apps/homework-wordcloud/sample_input/19990102.xlsx
+++ b/apps/homework-wordcloud/sample_input/19990102.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>重金屬污染的案例讓我印象深刻，污染一次要補救好幾十年。</t>
+          <t>重金屬污染的案例讓我印象深刻，污染一次要補救好幾十年。未來政策要怎麼防範？</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>重金屬污染的案例讓我印象深刻，污染一次要補救好幾十年。</t>
+          <t>重金屬污染的案例讓我印象深刻，污染一次要補救好幾十年。未來政策要怎麼防範？</t>
         </is>
       </c>
     </row>
